--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260926.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260926.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -715,7 +715,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12777,7 +12777,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13447,7 +13447,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14054,7 +14054,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -14992,7 +14992,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16399,7 +16399,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16667,7 +16667,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16935,7 +16935,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17337,7 +17337,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17605,7 +17605,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17672,7 +17672,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17739,7 +17739,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17806,7 +17806,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17940,7 +17940,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -18007,7 +18007,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18141,7 +18141,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18208,7 +18208,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18275,7 +18275,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18476,7 +18476,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18677,7 +18677,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18744,7 +18744,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18878,7 +18878,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19213,7 +19213,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19347,7 +19347,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19481,7 +19481,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19548,7 +19548,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19682,7 +19682,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19816,7 +19816,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20017,7 +20017,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20084,7 +20084,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20151,7 +20151,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20218,7 +20218,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20285,7 +20285,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20352,7 +20352,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20687,7 +20687,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20821,7 +20821,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20888,7 +20888,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21223,7 +21223,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21357,7 +21357,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21558,7 +21558,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21625,7 +21625,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21692,7 +21692,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21826,7 +21826,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21893,7 +21893,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22027,7 +22027,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22094,7 +22094,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22161,7 +22161,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22295,7 +22295,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22362,7 +22362,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22429,7 +22429,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22496,7 +22496,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S327" s="1" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S328" s="1" t="n">
@@ -22630,7 +22630,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S329" s="1" t="n">
@@ -22697,7 +22697,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S330" s="1" t="n">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S331" s="1" t="n">
@@ -22831,7 +22831,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S332" s="1" t="n">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S333" s="1" t="n">
@@ -22949,7 +22949,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S334" t="inlineStr"/>
@@ -22998,7 +22998,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S335" t="inlineStr"/>
@@ -23047,7 +23047,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S336" t="inlineStr"/>
@@ -23096,7 +23096,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>2026-09-26 08:48:40</t>
+          <t>2026-09-26 13:20:44</t>
         </is>
       </c>
       <c r="S337" t="inlineStr"/>
